--- a/data/indicadores/16_07_02_03_tcs.xlsx
+++ b/data/indicadores/16_07_02_03_tcs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60178AAE-4EC6-4C6A-A491-3E36AA2B4FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E9EA4DD-8A78-42D2-BB86-98E598A6D78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{1F0CCE29-C528-4204-AA1E-F32404105712}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="514">
   <si>
     <t>Depart</t>
   </si>
@@ -1563,13 +1563,19 @@
     <t>Conflictividad social (promedio 2022-2024)</t>
   </si>
   <si>
-    <t>Tasa de Conflictividad Social</t>
-  </si>
-  <si>
-    <t>ABSOLUTO (promedio 2018-2020)</t>
-  </si>
-  <si>
-    <t>ABSOLUTO (promedio 2022-2024)</t>
+    <t>Cantidad de conflictos (promedio 2018-2020)</t>
+  </si>
+  <si>
+    <t>Cantidad de conflictos (promedio 2022-2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantidad de conflictos </t>
+  </si>
+  <si>
+    <t>Absoluto_2024</t>
+  </si>
+  <si>
+    <t>Absoluto_2018</t>
   </si>
 </sst>
 </file>
@@ -2058,7 +2064,7 @@
         <v>499</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>500</v>
@@ -2076,7 +2082,7 @@
         <v>504</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="P1" s="9" t="s">
         <v>505</v>
@@ -22237,10 +22243,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -27064,7 +27070,7 @@
   <dimension ref="A1:D344"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>481</v>
       </c>
@@ -27072,10 +27078,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -30535,10 +30541,10 @@
         <v>483</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -30708,7 +30714,7 @@
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>482</v>
       </c>
@@ -30716,10 +30722,10 @@
         <v>483</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -30882,10 +30888,10 @@
         <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C2" s="1">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
